--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487196_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487196_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.472</v>
+        <v>3.3173</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2261</v>
+        <v>2.2856</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2459</v>
+        <v>1.0318</v>
       </c>
       <c r="G2" t="n">
         <v>1.9628</v>
@@ -610,13 +610,13 @@
         <v>3.6672</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3054</v>
+        <v>-0.46</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2195</v>
+        <v>0.279</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5249</v>
+        <v>-0.739</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6945</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.197</v>
+        <v>2.1515</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2641</v>
+        <v>1.2447</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1423</v>
+        <v>1.2966</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9500999999999999</v>
+        <v>0.6583</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0924</v>
+        <v>0.6383</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9966</v>
+        <v>1.4635</v>
       </c>
       <c r="K3" t="n">
-        <v>0.419</v>
+        <v>1.4799</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5777</v>
+        <v>-0.0164</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.1669</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3691</v>
+        <v>-0.8216</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5148</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>2.8951</v>
+        <v>2.7021</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.193</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0881</v>
+        <v>2.8951</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1263</v>
+        <v>-0.8246</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1745</v>
+        <v>-0.0257</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3009</v>
+        <v>-0.7988</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2859</v>
+        <v>-1.0226</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.0226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5239</v>
+        <v>2.1167</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6439</v>
+        <v>1.0231</v>
       </c>
       <c r="F4" t="n">
-        <v>0.88</v>
+        <v>1.0936</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2966</v>
+        <v>0.1423</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6583</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6383</v>
+        <v>1.0924</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4635</v>
+        <v>0.9966</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4799</v>
+        <v>0.419</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0164</v>
+        <v>0.5777</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1669</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8216</v>
+        <v>-1.3691</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.5148</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7021</v>
+        <v>2.8951</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.193</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8951</v>
+        <v>3.0881</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4522</v>
+        <v>-1.2066</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6266</v>
+        <v>-0.0664</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8256</v>
+        <v>-1.1402</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0226</v>
+        <v>0.2859</v>
       </c>
       <c r="W4" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-1.0226</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8205</v>
+        <v>1.4213</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4069</v>
+        <v>0.7668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4136</v>
+        <v>0.6545</v>
       </c>
       <c r="G5" t="n">
         <v>1.3767</v>
@@ -844,13 +844,13 @@
         <v>2.8951</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.2004</v>
+        <v>-1.5996</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7588</v>
+        <v>-0.3989</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4416</v>
+        <v>-1.2007</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2859</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3433</v>
+        <v>-0.1413</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1766</v>
+        <v>-1.7886</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5198</v>
+        <v>1.6473</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4041</v>
+        <v>2.423</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2742</v>
+        <v>1.7947</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.13</v>
+        <v>0.6283</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.1509</v>
+        <v>2.363</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.6461</v>
+        <v>2.3959</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5048</v>
+        <v>-0.0328</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2532</v>
+        <v>0.06</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.628</v>
+        <v>-0.6012</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3748</v>
+        <v>0.6612</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0881</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>-4.0532</v>
       </c>
       <c r="R6" t="n">
-        <v>4.0532</v>
+        <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5818</v>
+        <v>-0.5414</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9394</v>
+        <v>-0.0985</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3576</v>
+        <v>-0.4429</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.9225</v>
+        <v>-0.2859</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.9225</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7421</v>
+        <v>-1.5544</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3894</v>
+        <v>-2.6192</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6473</v>
+        <v>1.0647</v>
       </c>
       <c r="G7" t="n">
-        <v>2.423</v>
+        <v>-2.4041</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7947</v>
+        <v>-2.2742</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6283</v>
+        <v>-0.13</v>
       </c>
       <c r="J7" t="n">
-        <v>2.363</v>
+        <v>-2.1509</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3959</v>
+        <v>-1.6461</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0328</v>
+        <v>-0.5048</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06</v>
+        <v>-0.2532</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6012</v>
+        <v>-0.628</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6612</v>
+        <v>0.3748</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7371</v>
+        <v>3.0881</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.0532</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3161</v>
+        <v>4.0532</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1422</v>
+        <v>-0.3159</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6993</v>
+        <v>0.4968</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4429</v>
+        <v>-0.8127</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2859</v>
+        <v>-1.9225</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2859</v>
+        <v>-1.9225</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4277</v>
+        <v>-1.7222</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.673</v>
+        <v>-2.9139</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2453</v>
+        <v>1.1918</v>
       </c>
       <c r="G8" t="n">
         <v>-3.301</v>
@@ -1078,13 +1078,13 @@
         <v>3.0881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3477</v>
+        <v>-0.6421</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3979</v>
+        <v>0.157</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7456</v>
+        <v>-0.7992</v>
       </c>
       <c r="V8" t="n">
         <v>1.0629</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8618</v>
+        <v>-3.9665</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.7061</v>
+        <v>-4.1052</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1557</v>
+        <v>0.1388</v>
       </c>
       <c r="G9" t="n">
         <v>-6.4698</v>
@@ -1156,13 +1156,13 @@
         <v>4.0532</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.6552</v>
+        <v>-1.7599</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.043</v>
+        <v>-0.4421</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.6122</v>
+        <v>-1.3177</v>
       </c>
       <c r="V9" t="n">
         <v>2.3331</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.325100000000002</v>
+        <v>1.622400000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.4041</v>
+        <v>-6.1067</v>
       </c>
       <c r="F10" t="n">
-        <v>7.729200000000001</v>
+        <v>7.7293</v>
       </c>
       <c r="G10" t="n">
         <v>-4.9735</v>
@@ -1216,7 +1216,7 @@
         <v>-4.5445</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.2048</v>
+        <v>-4.204800000000001</v>
       </c>
       <c r="N10" t="n">
         <v>-8.0817</v>
@@ -1234,16 +1234,16 @@
         <v>26.0561</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.647600000000001</v>
+        <v>-7.350099999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3964000000000002</v>
+        <v>-0.0988</v>
       </c>
       <c r="U10" t="n">
-        <v>-7.251300000000001</v>
+        <v>-7.251200000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5295000000000003</v>
+        <v>-0.5295000000000001</v>
       </c>
       <c r="W10" t="n">
         <v>6.3413</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.2353</v>
+        <v>6.9891</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7751</v>
+        <v>3.2727</v>
       </c>
       <c r="F11" t="n">
-        <v>4.4602</v>
+        <v>3.7164</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2135</v>
+        <v>5.0072</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8861</v>
+        <v>0.1833</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6726</v>
+        <v>4.8239</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7916</v>
+        <v>3.6856</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7865</v>
+        <v>0.5846</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9949</v>
+        <v>3.101</v>
       </c>
       <c r="M11" t="n">
-        <v>1.422</v>
+        <v>1.3217</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09959999999999999</v>
+        <v>-0.4013</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3223</v>
+        <v>1.7229</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.6672</v>
+        <v>-0.772</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.7902</v>
+        <v>-2.8951</v>
       </c>
       <c r="R11" t="n">
         <v>2.1231</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5032</v>
+        <v>1.24</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6882</v>
+        <v>0.9684</v>
       </c>
       <c r="U11" t="n">
-        <v>1.815</v>
+        <v>0.2716</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1857</v>
+        <v>1.5138</v>
       </c>
       <c r="W11" t="n">
-        <v>2.0856</v>
+        <v>1.5138</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9453</v>
+        <v>4.038</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8707</v>
+        <v>0.2744</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0745</v>
+        <v>3.7635</v>
       </c>
       <c r="G12" t="n">
-        <v>5.0072</v>
+        <v>4.2135</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1833</v>
+        <v>4.8861</v>
       </c>
       <c r="I12" t="n">
-        <v>4.8239</v>
+        <v>-0.6726</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6856</v>
+        <v>2.7916</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5846</v>
+        <v>4.7865</v>
       </c>
       <c r="L12" t="n">
-        <v>3.101</v>
+        <v>-1.9949</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3217</v>
+        <v>1.422</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4013</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>1.7229</v>
+        <v>1.3223</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.772</v>
+        <v>-3.6672</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8951</v>
+        <v>-5.7902</v>
       </c>
       <c r="R12" t="n">
         <v>2.1231</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8038</v>
+        <v>2.3058</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4336</v>
+        <v>1.1875</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3702</v>
+        <v>1.1183</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5138</v>
+        <v>1.1857</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5138</v>
+        <v>2.0856</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6114</v>
+        <v>1.5881</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4135</v>
+        <v>-0.6894</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1978</v>
+        <v>2.2775</v>
       </c>
       <c r="G13" t="n">
         <v>1.9513</v>
@@ -1468,13 +1468,13 @@
         <v>0.772</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4973</v>
+        <v>1.474</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4398</v>
+        <v>1.3369</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0575</v>
+        <v>0.1371</v>
       </c>
       <c r="V13" t="n">
         <v>0.2859</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. NDIR</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.8098</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5907</v>
+        <v>-0.6279</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0862</v>
+        <v>-0.182</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3332</v>
+        <v>-0.1098</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6717</v>
+        <v>0.2629</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3385</v>
+        <v>-0.3727</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1939</v>
+        <v>1.1585</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1125</v>
+        <v>1.1178</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0814</v>
+        <v>0.0407</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8607</v>
+        <v>-1.2682</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4408</v>
+        <v>-0.8548</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4199</v>
+        <v>-0.4134</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.5091</v>
+        <v>-1.158</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.8602</v>
+        <v>-1.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0128</v>
+        <v>0.1299</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0755</v>
+        <v>0.1438</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9373</v>
+        <v>-0.0139</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5138</v>
+        <v>0.3281</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.5138</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>A. RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.3641</v>
+        <v>-1.5354</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1286</v>
+        <v>-1.3213</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2355</v>
+        <v>-0.2141</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1098</v>
+        <v>-2.1748</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2629</v>
+        <v>-0.8953</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3727</v>
+        <v>-1.2795</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1585</v>
+        <v>-0.7934</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1178</v>
+        <v>0.4604</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0407</v>
+        <v>-1.2538</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2682</v>
+        <v>-1.3814</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8548</v>
+        <v>-1.3557</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4134</v>
+        <v>-0.0257</v>
       </c>
       <c r="P15" t="n">
         <v>-1.158</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R15" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4244</v>
+        <v>0.8976</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3569</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0674</v>
+        <v>0.002</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3281</v>
+        <v>0.8999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.4716</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3281</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>M. NDIR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.3371</v>
+        <v>-1.946</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4069</v>
+        <v>-1.5921</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9302</v>
+        <v>-0.3539</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.3992</v>
+        <v>0.3332</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8248</v>
+        <v>0.6717</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5744</v>
+        <v>-0.3385</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.777</v>
+        <v>1.1939</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5175</v>
+        <v>1.1125</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2945</v>
+        <v>0.0814</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6222</v>
+        <v>-0.8607</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3423</v>
+        <v>-0.4408</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2799</v>
+        <v>-0.4199</v>
       </c>
       <c r="P16" t="n">
-        <v>0.386</v>
+        <v>-2.5091</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R16" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3239</v>
+        <v>1.7437</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3702</v>
+        <v>1.0741</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.694</v>
+        <v>0.6696</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RAMIREZ RUIZ</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.938</v>
+        <v>-2.0763</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3227</v>
+        <v>-0.3067</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6153</v>
+        <v>-1.7696</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1748</v>
+        <v>-2.3992</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8953</v>
+        <v>-0.8248</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2795</v>
+        <v>-1.5744</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7934</v>
+        <v>-0.777</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4604</v>
+        <v>0.5175</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2538</v>
+        <v>-1.2945</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3814</v>
+        <v>-1.6222</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3557</v>
+        <v>-1.3423</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0257</v>
+        <v>-0.2799</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7371</v>
+        <v>0.386</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.505</v>
+        <v>-0.0631</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1057</v>
+        <v>0.4703</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3993</v>
+        <v>-0.5334</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4716</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1255</v>
+        <v>-2.5907</v>
       </c>
       <c r="E18" t="n">
         <v>-3.086</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0395</v>
+        <v>0.4953</v>
       </c>
       <c r="G18" t="n">
         <v>0.3196</v>
@@ -1858,13 +1858,13 @@
         <v>1.7371</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3569</v>
+        <v>0.1778</v>
       </c>
       <c r="T18" t="n">
         <v>0.472</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8289</v>
+        <v>-0.2942</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.6755</v>
+        <v>-3.6467</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.2539</v>
+        <v>-3.653</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4216</v>
+        <v>0.0064</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1677</v>
@@ -1936,13 +1936,13 @@
         <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0482</v>
+        <v>1.0771</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1018</v>
+        <v>0.7027</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0536</v>
+        <v>0.3744</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1701</v>
@@ -1969,16 +1969,16 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.325100000000003</v>
+        <v>0.01030000000000175</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.7295</v>
+        <v>-7.7293</v>
       </c>
       <c r="F20" t="n">
-        <v>6.404200000000001</v>
+        <v>7.7395</v>
       </c>
       <c r="G20" t="n">
-        <v>4.9733</v>
+        <v>4.973300000000001</v>
       </c>
       <c r="H20" t="n">
         <v>4.3057</v>
@@ -1987,7 +1987,7 @@
         <v>0.6676999999999995</v>
       </c>
       <c r="J20" t="n">
-        <v>4.204999999999999</v>
+        <v>4.205</v>
       </c>
       <c r="K20" t="n">
         <v>8.081900000000001</v>
@@ -1996,7 +1996,7 @@
         <v>-3.8769</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7686999999999997</v>
+        <v>0.7687000000000002</v>
       </c>
       <c r="N20" t="n">
         <v>-3.776</v>
@@ -2014,16 +2014,16 @@
         <v>11.5805</v>
       </c>
       <c r="S20" t="n">
-        <v>7.6475</v>
+        <v>8.982799999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>7.2513</v>
+        <v>7.2514</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3964000000000002</v>
+        <v>1.7315</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5295000000000001</v>
+        <v>0.5294999999999996</v>
       </c>
       <c r="W20" t="n">
         <v>6.8708</v>
